--- a/handlers.xlsx
+++ b/handlers.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,8 +439,6 @@
           <t>timeOut:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -448,8 +446,11 @@
           <t xml:space="preserve">  - Кажется, вы отлучились. Если у вас появятся еще вопросы, буду рад помочь с ответом.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Кажется, вы отлучились. Если у вас появятся еще вопросы, буду рад помочь с ответом.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -457,26 +458,19 @@
           <t xml:space="preserve">  - Похоже, вы отлучились. Если будут вопросы, напишите мне.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Похоже, вы отлучились. Если будут вопросы, напишите мне.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>anyError:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -486,10 +480,9 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - К сожалению, произошла техническая ошибка. Пожалуйста, обратитесь на горячую линию банка по номеру 8-800-250-57-57.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>К сожалению, произошла техническая ошибка. Пожалуйста, обратитесь на горячую линию банка по номеру 8-800-250-57-57.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -499,28 +492,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Возникла техническая ошибка. Пожалуйста, для продолжения консультации обратитесь на горячую линию банка по номеру 8-800-250-57-57.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+          <t>Возникла техническая ошибка. Пожалуйста, для продолжения консультации обратитесь на горячую линию банка по номеру 8-800-250-57-57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>limitHandler:</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -528,8 +510,6 @@
           <t xml:space="preserve">  firstReplies:</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -537,8 +517,11 @@
           <t xml:space="preserve">    - Не уверен, что понял вас. Можете переформулировать вопрос?</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Не уверен, что понял вас. Можете переформулировать вопрос?</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -546,8 +529,11 @@
           <t xml:space="preserve">    - Прошу прощения, я не совсем понял вас. Пожалуйста, сформулируйте вашу мысль более кратко.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Прошу прощения, я не совсем понял вас. Пожалуйста, сформулируйте вашу мысль более кратко.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -555,26 +541,19 @@
           <t xml:space="preserve">  finalReply: Это за пределами моих возможностей, но я уже зову на помощь оператора!</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Это за пределами моих возможностей, но я уже зову на помощь оператора!</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>scriptAndDialogError:</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -582,8 +561,6 @@
           <t xml:space="preserve">  firstReplies:</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -591,8 +568,11 @@
           <t xml:space="preserve">    - Извините, не получается вас понять. Перефразируйте, пожалуйста, более коротко то, что вы хотели сказать.</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Извините, не получается вас понять. Перефразируйте, пожалуйста, более коротко то, что вы хотели сказать.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -600,8 +580,11 @@
           <t xml:space="preserve">    - Простите, я не совсем понял вас. Пожалуйста, сформулируйте вашу мысль более кратко.</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Простите, я не совсем понял вас. Пожалуйста, сформулируйте вашу мысль более кратко.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -609,26 +592,24 @@
           <t xml:space="preserve">  finalReply: Сожалею, что не могу помочь сам. Но рядом есть человек, который точно разберется – подключаю.</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Пустой текст</t>
-        </is>
-      </c>
-    </row>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Сожалею, что не могу помочь сам. Но рядом есть человек, который точно разберется — подключаю.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>эн-дефис (–) заменён на тире (—) для единообразия</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>obscene:</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -636,8 +617,11 @@
           <t xml:space="preserve">  - Я верю, что мы найдем решение в рамках общепринятой манеры общения.</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Я верю, что мы найдем решение в рамках общепринятой манеры общения.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -645,8 +629,11 @@
           <t xml:space="preserve">  - Понимаю ваше возмущение, но прошу вести беседу в конструктивном ключе.</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Понимаю ваше возмущение, но прошу вести беседу в конструктивном ключе.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -654,8 +641,11 @@
           <t xml:space="preserve">  - Прошу вас выражаться корректнее, иначе мне будет сложно вам помочь.</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Прошу вас выражаться корректнее, иначе мне будет сложно вам помочь.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
